--- a/Automation_Test_Report.xlsx
+++ b/Automation_Test_Report.xlsx
@@ -46673,7 +46673,7 @@
       </c>
       <c r="F1642" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1828ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1926ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -47321,7 +47321,7 @@
       </c>
       <c r="F1665" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1713ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1728ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -47969,7 +47969,7 @@
       </c>
       <c r="F1688" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1553ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1590ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -48617,7 +48617,7 @@
       </c>
       <c r="F1711" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1804ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1871ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -49265,7 +49265,7 @@
       </c>
       <c r="F1734" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1703ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1793ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -49913,7 +49913,7 @@
       </c>
       <c r="F1757" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1884ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1885ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -50561,7 +50561,7 @@
       </c>
       <c r="F1780" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1615ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1655ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -51209,7 +51209,7 @@
       </c>
       <c r="F1803" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1687ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1587ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -51857,7 +51857,7 @@
       </c>
       <c r="F1826" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1885ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1661ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -52505,7 +52505,7 @@
       </c>
       <c r="F1849" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1736ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1931ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -53153,7 +53153,7 @@
       </c>
       <c r="F1872" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1701ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1734ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -53801,7 +53801,7 @@
       </c>
       <c r="F1895" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1761ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1572ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -54449,7 +54449,7 @@
       </c>
       <c r="F1918" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1783ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1920ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -55097,7 +55097,7 @@
       </c>
       <c r="F1941" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1895ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1930ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -55745,7 +55745,7 @@
       </c>
       <c r="F1964" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1821ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1607ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -56393,7 +56393,7 @@
       </c>
       <c r="F1987" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1833ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1732ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -57041,7 +57041,7 @@
       </c>
       <c r="F2010" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1725ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1558ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>

--- a/Automation_Test_Report.xlsx
+++ b/Automation_Test_Report.xlsx
@@ -46673,7 +46673,7 @@
       </c>
       <c r="F1642" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1926ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1781ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -47321,7 +47321,7 @@
       </c>
       <c r="F1665" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1728ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1879ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -47969,7 +47969,7 @@
       </c>
       <c r="F1688" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1590ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1871ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -48617,7 +48617,7 @@
       </c>
       <c r="F1711" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1871ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1793ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -49265,7 +49265,7 @@
       </c>
       <c r="F1734" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1793ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1623ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -49913,7 +49913,7 @@
       </c>
       <c r="F1757" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1885ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1841ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -50561,7 +50561,7 @@
       </c>
       <c r="F1780" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1655ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1930ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -51209,7 +51209,7 @@
       </c>
       <c r="F1803" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1587ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1738ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -51857,7 +51857,7 @@
       </c>
       <c r="F1826" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1661ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1609ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -52505,7 +52505,7 @@
       </c>
       <c r="F1849" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1931ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1585ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -53153,7 +53153,7 @@
       </c>
       <c r="F1872" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1734ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1874ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -53801,7 +53801,7 @@
       </c>
       <c r="F1895" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1572ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1743ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -54449,7 +54449,7 @@
       </c>
       <c r="F1918" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1920ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1640ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -55097,7 +55097,7 @@
       </c>
       <c r="F1941" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1930ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1706ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -55745,7 +55745,7 @@
       </c>
       <c r="F1964" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1607ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1558ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -56393,7 +56393,7 @@
       </c>
       <c r="F1987" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1732ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1580ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -57041,7 +57041,7 @@
       </c>
       <c r="F2010" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1558ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1714ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
